--- a/output/pdf_financials_xlsx/ISC.xlsx
+++ b/output/pdf_financials_xlsx/ISC.xlsx
@@ -853,34 +853,34 @@
         <v>55.73</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>67.929</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>71.694</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>96.349</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>105.342</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>106.055</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>122.625</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>143.7</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>166.547</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>196.495</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0</v>
+        <v>204.116</v>
       </c>
     </row>
     <row r="11">
@@ -902,34 +902,34 @@
         <v>21.633</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>84.789</v>
+        <v>16.86</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>89.45099999999999</v>
+        <v>17.757</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>94.047</v>
+        <v>-2.302</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>101.797</v>
+        <v>-3.545</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>105.452</v>
+        <v>-0.603</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>129.02</v>
+        <v>6.395</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>140.68</v>
+        <v>-3.02</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>159.133</v>
+        <v>-7.414</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>187.446</v>
+        <v>-9.048999999999999</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>202.374</v>
+        <v>-1.742</v>
       </c>
     </row>
     <row r="12">
@@ -939,46 +939,46 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.212</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>25.804</v>
+        <v>-0.237</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>25.151</v>
+        <v>-0.306</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>22.588</v>
+        <v>-0.331</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.256</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.369</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.416</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.283</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.172</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.463</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>1.163</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.906</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.531</v>
       </c>
     </row>
     <row r="13">
@@ -1802,46 +1802,46 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>21.325</v>
+        <v>21.452</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.675</v>
+        <v>25.366</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.214</v>
+        <v>25.671</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.157</v>
+        <v>23.076</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>20.779</v>
+        <v>20.523</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>37.439</v>
+        <v>37.07</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>25.576</v>
+        <v>25.16</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>26.38</v>
+        <v>26.097</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>28.623</v>
+        <v>28.451</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>44.081</v>
+        <v>43.941</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>43.018</v>
+        <v>42.555</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>34.79</v>
+        <v>33.627</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>28.925</v>
+        <v>28.019</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>36.853</v>
+        <v>36.322</v>
       </c>
     </row>
     <row r="28">
@@ -1900,46 +1900,46 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>28.964</v>
+        <v>29.091</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>4.83</v>
+        <v>30.871</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>5.303</v>
+        <v>30.76</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>5.87</v>
+        <v>28.789</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>29.208</v>
+        <v>28.952</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>44.946</v>
+        <v>44.577</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>37.351</v>
+        <v>36.935</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>37.78</v>
+        <v>37.497</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>41.347</v>
+        <v>41.175</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>57.859</v>
+        <v>57.719</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>57.753</v>
+        <v>57.29</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>55.296</v>
+        <v>54.133</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>56.498</v>
+        <v>55.592</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>62.576</v>
+        <v>62.045</v>
       </c>
     </row>
     <row r="30">
@@ -1949,46 +1949,46 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>38.50776430546692</v>
+        <v>38.67661135928525</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>6.103802555256474</v>
+        <v>39.01252353691979</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>6.590934513230342</v>
+        <v>38.23065163623709</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>7.49508414413034</v>
+        <v>36.75911029392987</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>33.05007072135785</v>
+        <v>32.76039603960396</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>48.0233353278058</v>
+        <v>47.62907086075733</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>31.35288044253804</v>
+        <v>31.00368501901268</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>28.41285121232176</v>
+        <v>28.20001804945551</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>30.24143706618491</v>
+        <v>30.11563526253813</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>34.1594884844048</v>
+        <v>34.07683360983357</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>30.41312304168093</v>
+        <v>30.16930408910187</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>25.77661756479582</v>
+        <v>25.23447697184412</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>22.83984056014165</v>
+        <v>22.4735816563311</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>24.27628158872776</v>
+        <v>24.07028079731229</v>
       </c>
     </row>
     <row r="31">
@@ -2103,43 +2103,43 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>21.138</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>27.614</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>33.581</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>36.571</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>33.533</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>31.265</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>31.265</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>28.651</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>23.731</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>40.104</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>34.479</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>24.193</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>20.994</v>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
@@ -2205,43 +2205,43 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>21.138</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>27.614</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>33.581</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>36.571</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.15</v>
+        <v>33.683</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.301</v>
+        <v>31.566</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.301</v>
+        <v>31.566</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.448</v>
+        <v>29.099</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.475</v>
+        <v>24.206</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.036</v>
+        <v>40.14</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>34.479</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>24.193</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>20.994</v>
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
@@ -2817,43 +2817,43 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>21.779</v>
+        <v>0.641</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>28.454</v>
+        <v>0.84</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>34.503</v>
+        <v>0.922</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>38.966</v>
+        <v>2.395</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>36.439</v>
+        <v>2.906</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>33.178</v>
+        <v>1.913</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>33.178</v>
+        <v>1.913</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>32.161</v>
+        <v>3.51</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>29.21</v>
+        <v>5.479</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>43.64</v>
+        <v>3.536</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>42.283</v>
+        <v>7.804</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>32.659</v>
+        <v>8.465999999999999</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>30.79</v>
+        <v>9.795999999999999</v>
       </c>
       <c r="O48" s="1" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11582,7 +11582,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -14368,7 +14368,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -17340,7 +17340,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
@@ -37934,7 +37934,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -38070,7 +38070,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -38150,7 +38150,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -39528,7 +39528,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -40854,7 +40854,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -40940,7 +40940,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -41540,7 +41540,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -42550,7 +42550,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -42638,7 +42638,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -43668,7 +43668,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -43756,7 +43756,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E435" s="5" t="n">
@@ -45536,7 +45536,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E456" s="5" t="n">

--- a/output/pdf_financials_xlsx/ISC.xlsx
+++ b/output/pdf_financials_xlsx/ISC.xlsx
@@ -792,46 +792,46 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>4.476</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>4.202</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>4.316</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>4.563</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>4.992</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0</v>
+        <v>5.293</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0</v>
+        <v>3.369</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0</v>
+        <v>3.485</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0</v>
+        <v>3.004</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0</v>
+        <v>4.003</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0</v>
+        <v>4.648</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0</v>
+        <v>4.494</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>0</v>
+        <v>4.726</v>
       </c>
     </row>
     <row r="10">
@@ -1000,34 +1000,34 @@
         <v>-0</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0</v>
+        <v>0.321</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0</v>
+        <v>0.507</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-0</v>
+        <v>0.773</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>1.246</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>2.045</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-0</v>
+        <v>2.673</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>-0</v>
+        <v>3.177</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>-0</v>
+        <v>13.183</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>-0</v>
+        <v>21.946</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>-0</v>
+        <v>16.797</v>
       </c>
     </row>
     <row r="14">
@@ -1814,34 +1814,34 @@
         <v>23.076</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>20.523</v>
+        <v>20.202</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>37.07</v>
+        <v>36.563</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>25.16</v>
+        <v>24.387</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>26.097</v>
+        <v>24.851</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>28.451</v>
+        <v>26.406</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>43.941</v>
+        <v>41.268</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>42.555</v>
+        <v>39.378</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>33.627</v>
+        <v>20.444</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>28.019</v>
+        <v>6.073</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>36.322</v>
+        <v>19.525</v>
       </c>
     </row>
     <row r="28">
@@ -1912,34 +1912,34 @@
         <v>28.789</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>28.952</v>
+        <v>28.631</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>44.577</v>
+        <v>44.07</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>36.935</v>
+        <v>36.162</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>37.497</v>
+        <v>36.251</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>41.175</v>
+        <v>39.13</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>57.719</v>
+        <v>55.046</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>57.29</v>
+        <v>54.113</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>54.133</v>
+        <v>40.95</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>55.592</v>
+        <v>33.646</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>62.045</v>
+        <v>45.248</v>
       </c>
     </row>
     <row r="30">
@@ -1961,34 +1961,34 @@
         <v>36.75911029392987</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>32.76039603960396</v>
+        <v>32.397171145686</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>47.62907086075733</v>
+        <v>47.08735789383708</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>31.00368501901268</v>
+        <v>30.3548194844331</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>28.20001804945551</v>
+        <v>27.26295048432706</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>30.11563526253813</v>
+        <v>28.61991032964461</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>34.07683360983357</v>
+        <v>32.49871589748434</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>30.16930408910187</v>
+        <v>28.49627425682614</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>25.23447697184412</v>
+        <v>19.08912921872087</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>22.4735816563311</v>
+        <v>13.60170759118068</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>24.07028079731229</v>
+        <v>17.55390548016418</v>
       </c>
     </row>
     <row r="31">
@@ -6070,10 +6070,10 @@
         <v>0</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="O112" s="3" t="n">
         <v>0</v>
@@ -24498,7 +24498,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -24668,7 +24672,11 @@
           <t>Additions to intangible assets 8</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
@@ -27380,7 +27388,11 @@
           <t>Additions to intangible assets 8</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -28718,7 +28730,11 @@
           <t>Additions to intangible assets 9</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E254" s="5" t="n">
         <v>-5.295</v>
       </c>
@@ -30606,7 +30622,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -37686,7 +37706,11 @@
           <t>Occupancy costs</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr"/>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E361" s="5" t="n">
         <v>4.476</v>
       </c>
@@ -38232,7 +38256,11 @@
           <t>Net finance expense</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr"/>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E369" t="inlineStr">
         <is>
           <t>-</t>
@@ -40198,7 +40226,11 @@
           <t>Net finance (expense)</t>
         </is>
       </c>
-      <c r="D393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E393" t="inlineStr">
         <is>
           <t>-</t>
@@ -42724,7 +42756,11 @@
           <t>Net finance (expense)</t>
         </is>
       </c>
-      <c r="D423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E423" t="inlineStr">
         <is>
           <t>-</t>
